--- a/artfynd/A 18425-2026 artfynd.xlsx
+++ b/artfynd/A 18425-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137436410</v>
       </c>
       <c r="B2" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>137433811</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
